--- a/Students/ZRS2502/ZRS2502_Grade.xlsx
+++ b/Students/ZRS2502/ZRS2502_Grade.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\МТУСИ\Введение в ИТ\ЗРС2502\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Сергей\Documents\GitHub\MTUCI_Labs\Students\ZRS2502\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A13D7DB6-F24E-4ACC-BC91-37BF632628E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFE764C4-25E8-4738-A816-8EE867E392AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="36">
   <si>
     <t>ФИО</t>
   </si>
@@ -105,9 +105,6 @@
     <t>Шебанин Федор Александрович</t>
   </si>
   <si>
-    <t>?</t>
-  </si>
-  <si>
     <t>Задание №1</t>
   </si>
   <si>
@@ -115,9 +112,6 @@
   </si>
   <si>
     <t>Дополнительное</t>
-  </si>
-  <si>
-    <t>?+</t>
   </si>
   <si>
     <t>№ варианта</t>
@@ -168,7 +162,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,6 +172,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -288,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -303,6 +303,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -631,85 +637,85 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="11"/>
+      <c r="E1" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="11"/>
+      <c r="G1" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="H1" s="11"/>
+      <c r="I1" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" s="11"/>
+      <c r="K1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="L1" s="11"/>
+      <c r="M1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="N1" s="11"/>
+      <c r="O1" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="P1" s="13"/>
+    </row>
+    <row r="2" spans="1:16" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="15"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="9"/>
-      <c r="E1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="9"/>
-      <c r="G1" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J1" s="9"/>
-      <c r="K1" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="L1" s="9"/>
-      <c r="M1" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="N1" s="9"/>
-      <c r="O1" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="P1" s="11"/>
-    </row>
-    <row r="2" spans="1:16" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="13"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="E2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="G2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H2" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="I2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="K2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="M2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="O2" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="7" t="s">
         <v>28</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.4">
@@ -719,10 +725,37 @@
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="C3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="O3" s="9" t="s">
         <v>4</v>
       </c>
     </row>
@@ -734,10 +767,10 @@
       <c r="B4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="C4" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -749,11 +782,11 @@
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>30</v>
+      <c r="C5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.4">
@@ -764,10 +797,10 @@
       <c r="B6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="C6" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -779,8 +812,8 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>26</v>
+      <c r="C7" s="8" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.4">
@@ -791,10 +824,10 @@
       <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="C8" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -806,11 +839,11 @@
       <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>26</v>
+      <c r="C9" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.4">
@@ -821,11 +854,11 @@
       <c r="B10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>30</v>
+      <c r="C10" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.4">
@@ -836,10 +869,10 @@
       <c r="B11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="C11" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -851,8 +884,8 @@
       <c r="B12" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>30</v>
+      <c r="C12" s="8" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.4">
@@ -863,8 +896,8 @@
       <c r="B13" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="3" t="s">
-        <v>26</v>
+      <c r="C13" s="8" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.4">
@@ -884,10 +917,10 @@
       <c r="B15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="C15" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -908,10 +941,10 @@
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="3" t="s">
+      <c r="C17" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -923,11 +956,11 @@
       <c r="B18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>26</v>
+      <c r="C18" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.4">
@@ -938,10 +971,10 @@
       <c r="B19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="C19" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -953,10 +986,10 @@
       <c r="B20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="3" t="s">
+      <c r="C20" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -977,10 +1010,10 @@
       <c r="B22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="3" t="s">
+      <c r="C22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="8" t="s">
         <v>4</v>
       </c>
     </row>
@@ -992,11 +1025,11 @@
       <c r="B23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>30</v>
+      <c r="C23" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.4">
@@ -1016,10 +1049,10 @@
       <c r="B25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="3" t="s">
+      <c r="C25" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="8" t="s">
         <v>4</v>
       </c>
     </row>
